--- a/data/trans_dic/IP19C06-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP19C06-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por tratamiento de las enfermedades de las encías</t>
+          <t>Menores que en su última visita al dentista fue por tratamiento de las enfermedades de las encías (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,4</t>
+          <t>0,0; 3,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,62</t>
+          <t>0,0; 6,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,76</t>
+          <t>0,0; 5,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,11</t>
+          <t>0,0; 3,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,68</t>
+          <t>0,0; 7,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>0,0; 2,75</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,57</t>
+          <t>0,0; 3,1</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 5,0</t>
+          <t>0,27; 4,39</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 2,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,89</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,01</t>
+          <t>0,55; 5,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,36</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,25</t>
+          <t>0,26; 2,43</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,85</t>
+          <t>0,29; 4,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,18</t>
+          <t>0,0; 2,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,99</t>
+          <t>0,36; 3,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 2,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,82</t>
+          <t>0,0; 3,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,63</t>
+          <t>0,0; 2,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,21</t>
+          <t>0,0; 3,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,35</t>
+          <t>0,0; 1,23</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,58</t>
+          <t>0,43; 2,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,65</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,19</t>
+          <t>0,18; 2,1</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,0</t>
+          <t>0,32; 2,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,66</t>
+          <t>0,68; 2,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,2</t>
+          <t>0,0; 1,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,78</t>
+          <t>0,01; 1,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 0,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,62</t>
+          <t>0,0; 0,73</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,38</t>
+          <t>0,35; 1,44</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,76</t>
+          <t>0,08; 0,84</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,59</t>
+          <t>0,49; 1,76</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por tratamiento de las enfermedades de las encías (tasa de respuesta: 99,46%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>931</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>742</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1045</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1324</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1976</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2932</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4397</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3376</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3383</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5562</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4661</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4652</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>389; 6290</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3088</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>675; 6123</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3906</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>741; 6980</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2259</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1481</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1332</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3431</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>1317</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3591</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>431; 6061</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3456</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>712; 6158</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4745</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4928</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3796</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 7496</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4137</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>1250; 7386</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4680</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>782; 9142</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3230</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>5758</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2223</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2377</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>5452</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2088</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>8135</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1127; 7336</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4644</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2657; 10494</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3836</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>18; 6120</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3520</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 8558</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5225</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2505; 10386</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>619; 6144</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>4279; 15396</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C06-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP19C06-Edad-trans_dic.xlsx
@@ -862,17 +862,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,77</t>
+          <t>0,0; 3,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,46</t>
+          <t>0,0; 5,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,1</t>
+          <t>0,0; 5,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,67</t>
+          <t>0,0; 4,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,21</t>
+          <t>0,0; 6,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,75</t>
+          <t>0,0; 2,66</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,1</t>
+          <t>0,0; 2,57</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 4,39</t>
+          <t>0,27; 4,4</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,47</t>
+          <t>0,0; 2,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,02</t>
+          <t>0,56; 4,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,37</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,43</t>
+          <t>0,23; 2,2</t>
         </is>
       </c>
     </row>
@@ -1142,42 +1142,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 4,1</t>
+          <t>0,29; 4,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,38</t>
+          <t>0,0; 2,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,11</t>
+          <t>0,35; 2,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,73</t>
+          <t>0,0; 2,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,49</t>
+          <t>0,0; 3,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,81</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,16</t>
+          <t>0,0; 2,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,23</t>
+          <t>0,0; 1,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,0; 1,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,1</t>
+          <t>0,18; 2,06</t>
         </is>
       </c>
     </row>
@@ -1282,32 +1282,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,07</t>
+          <t>0,32; 2,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,68</t>
+          <t>0,71; 2,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 1,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 1,67</t>
+          <t>0,17; 1,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1317,22 +1317,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,73</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,44</t>
+          <t>0,35; 1,43</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,84</t>
+          <t>0,08; 0,82</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,76</t>
+          <t>0,47; 1,73</t>
         </is>
       </c>
     </row>
@@ -1858,17 +1858,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2932</t>
+          <t>0; 2876</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4397</t>
+          <t>0; 3945</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3376</t>
+          <t>0; 3326</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3383</t>
+          <t>0; 3821</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5562</t>
+          <t>0; 4750</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 4661</t>
+          <t>0; 4522</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 4652</t>
+          <t>0; 3863</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>389; 6290</t>
+          <t>387; 6305</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3088</t>
+          <t>0; 3523</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>675; 6123</t>
+          <t>681; 6065</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 3906</t>
+          <t>0; 3529</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>741; 6980</t>
+          <t>671; 6307</t>
         </is>
       </c>
     </row>
@@ -2274,57 +2274,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>431; 6061</t>
+          <t>429; 6123</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3456</t>
+          <t>0; 3197</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>712; 6158</t>
+          <t>698; 5893</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4745</t>
+          <t>0; 4335</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4928</t>
+          <t>0; 5062</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3796</t>
+          <t>0; 2843</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 7496</t>
+          <t>0; 6631</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4137</t>
+          <t>0; 4072</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1250; 7386</t>
+          <t>1241; 7374</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 4680</t>
+          <t>0; 4101</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>782; 9142</t>
+          <t>776; 8957</t>
         </is>
       </c>
     </row>
@@ -2482,57 +2482,57 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1127; 7336</t>
+          <t>1128; 7279</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4644</t>
+          <t>0; 4974</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2657; 10494</t>
+          <t>2765; 11093</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3836</t>
+          <t>0; 4001</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18; 6120</t>
+          <t>622; 6206</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3520</t>
+          <t>0; 3513</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 8558</t>
+          <t>0; 8563</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 5225</t>
+          <t>0; 4522</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2505; 10386</t>
+          <t>2520; 10312</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>619; 6144</t>
+          <t>612; 5975</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4279; 15396</t>
+          <t>4082; 15143</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C06-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP19C06-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -794,44 +794,44 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>0,75%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>1,13%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0,78%</t>
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,7</t>
+          <t>0,0; 4,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,8</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,02</t>
+          <t>0,0; 7,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,17 +882,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,15</t>
+          <t>0,0; 4,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,16</t>
+          <t>0,0; 4,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,66</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 4,4</t>
+          <t>0,27; 5,01</t>
         </is>
       </c>
     </row>
@@ -934,37 +934,37 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>0,56%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,55; 5,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,2</t>
+          <t>0,27; 2,25</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1,32%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 4,14</t>
+          <t>0,0; 3,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,2</t>
+          <t>0,0; 2,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,98</t>
+          <t>0,0; 1,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,59</t>
+          <t>0,29; 3,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,1</t>
+          <t>0,0; 2,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,8</t>
+          <t>0,37; 3,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,55</t>
+          <t>0,44; 2,58</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,46</t>
+          <t>0,0; 1,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,06</t>
+          <t>0,18; 1,71</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,06</t>
+          <t>0,17; 1,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,83</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,7</t>
+          <t>0,32; 2,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>0,7; 2,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,63</t>
+          <t>0,0; 0,62</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,43</t>
+          <t>0,34; 1,38</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,82</t>
+          <t>0,0; 0,76</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,73</t>
+          <t>0,42; 1,46</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1727,32 +1727,32 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1790,37 +1790,37 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>742</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>964</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>582</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>771</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>931</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>742</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>819</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>1783</t>
         </is>
       </c>
     </row>
@@ -1858,17 +1858,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2876</t>
+          <t>0; 3784</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3945</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3326</t>
+          <t>0; 5164</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1878,17 +1878,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3821</t>
+          <t>0; 3419</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3827</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4750</t>
+          <t>0; 2723</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 4522</t>
+          <t>0; 4655</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 3863</t>
+          <t>0; 3866</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>387; 6305</t>
+          <t>349; 6559</t>
         </is>
       </c>
     </row>
@@ -1930,37 +1930,37 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1998,29 +1998,29 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>698</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2568</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2507</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3523</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>681; 6065</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3205</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>666; 6151</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 3529</t>
+          <t>0; 3499</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>671; 6307</t>
+          <t>743; 6246</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,49 +2201,49 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>1481</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>1950</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>617</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2259</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2363</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1219</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1481</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1332</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1219</t>
-        </is>
-      </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
           <t>3431</t>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3003</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4529</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>429; 6123</t>
+          <t>0; 5387</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3197</t>
+          <t>0; 3557</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>698; 5893</t>
+          <t>0; 3738</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4335</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5062</t>
+          <t>430; 5700</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2843</t>
+          <t>0; 3170</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 6631</t>
+          <t>754; 6224</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4072</t>
+          <t>0; 4546</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1241; 7374</t>
+          <t>1258; 7468</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 4101</t>
+          <t>0; 4627</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>776; 8957</t>
+          <t>783; 7478</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,49 +2409,49 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>2223</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1605</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
           <t>3230</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>1388</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>5758</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>1219</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2223</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2377</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>1219</t>
-        </is>
-      </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
           <t>5452</t>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8135</t>
+          <t>7294</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4350</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1128; 7279</t>
+          <t>616; 6517</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4974</t>
+          <t>0; 3503</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2765; 11093</t>
+          <t>0; 5834</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4001</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>622; 6206</t>
+          <t>1142; 7087</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3513</t>
+          <t>0; 5418</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 8563</t>
+          <t>2789; 10451</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4522</t>
+          <t>0; 4387</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2520; 10312</t>
+          <t>2413; 9915</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>612; 5975</t>
+          <t>0; 5556</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4082; 15143</t>
+          <t>3587; 12528</t>
         </is>
       </c>
     </row>
